--- a/ML/DF_simulacao.xlsx
+++ b/ML/DF_simulacao.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,29 +435,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Real</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Simulado</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Erro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46112.33333333334</v>
       </c>
       <c r="B2" t="n">
@@ -457,91 +471,91 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46112.33402777778</v>
       </c>
       <c r="B3" t="n">
         <v>1.57</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5645</v>
+        <v>1.5632</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0055</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46112.33472222222</v>
       </c>
       <c r="B4" t="n">
         <v>1.57</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5619</v>
+        <v>1.561</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0081</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46112.33541666667</v>
       </c>
       <c r="B5" t="n">
         <v>1.57</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5558</v>
+        <v>1.5555</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0142</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46112.33611111111</v>
       </c>
       <c r="B6" t="n">
         <v>1.56</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5571</v>
+        <v>1.556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0029</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46112.33680555555</v>
       </c>
       <c r="B7" t="n">
         <v>1.56</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5518</v>
+        <v>1.5534</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46112.3375</v>
       </c>
       <c r="B8" t="n">
         <v>1.56</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5458</v>
+        <v>1.5509</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0142</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46112.33819444444</v>
       </c>
       <c r="B9" t="n">
@@ -555,7 +569,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46112.33888888889</v>
       </c>
       <c r="B10" t="n">
@@ -569,7 +583,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46112.33958333333</v>
       </c>
       <c r="B11" t="n">
@@ -583,7 +597,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46112.34027777778</v>
       </c>
       <c r="B12" t="n">
@@ -597,7 +611,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46112.34097222222</v>
       </c>
       <c r="B13" t="n">
@@ -611,49 +625,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46112.34166666667</v>
       </c>
       <c r="B14" t="n">
         <v>1.55</v>
       </c>
       <c r="C14" t="n">
-        <v>1.55</v>
+        <v>1.5502</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46112.34236111111</v>
       </c>
       <c r="B15" t="n">
         <v>1.55</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5558</v>
+        <v>1.5552</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0058</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46112.34305555555</v>
       </c>
       <c r="B16" t="n">
         <v>1.55</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5556</v>
+        <v>1.5568</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0056</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46112.34375</v>
       </c>
       <c r="B17" t="n">
@@ -667,21 +681,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46112.34444444445</v>
       </c>
       <c r="B18" t="n">
         <v>1.55</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5578</v>
+        <v>1.5583</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46112.34513888889</v>
       </c>
       <c r="B19" t="n">
@@ -695,7 +709,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46112.34583333333</v>
       </c>
       <c r="B20" t="n">
@@ -709,7 +723,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46112.34652777778</v>
       </c>
       <c r="B21" t="n">
@@ -723,21 +737,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46112.34722222222</v>
       </c>
       <c r="B22" t="n">
         <v>1.56</v>
       </c>
       <c r="C22" t="n">
-        <v>1.56</v>
+        <v>1.5601</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46112.34791666667</v>
       </c>
       <c r="B23" t="n">
@@ -751,259 +765,259 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46112.34861111111</v>
       </c>
       <c r="B24" t="n">
         <v>1.56</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5606</v>
+        <v>1.5614</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46112.34930555556</v>
       </c>
       <c r="B25" t="n">
         <v>1.56</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5609</v>
+        <v>1.5637</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0009</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46112.35</v>
       </c>
       <c r="B26" t="n">
         <v>1.56</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5648</v>
+        <v>1.5667</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0048</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46112.35069444445</v>
       </c>
       <c r="B27" t="n">
         <v>1.56</v>
       </c>
       <c r="C27" t="n">
-        <v>1.568</v>
+        <v>1.5668</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46112.35138888889</v>
       </c>
       <c r="B28" t="n">
         <v>1.56</v>
       </c>
       <c r="C28" t="n">
-        <v>1.5702</v>
+        <v>1.5671</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0102</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46112.35208333333</v>
       </c>
       <c r="B29" t="n">
         <v>1.56</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5701</v>
+        <v>1.5672</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0101</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46112.35277777778</v>
       </c>
       <c r="B30" t="n">
         <v>1.56</v>
       </c>
       <c r="C30" t="n">
-        <v>1.5701</v>
+        <v>1.5684</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0101</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46112.35347222222</v>
       </c>
       <c r="B31" t="n">
         <v>1.57</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5707</v>
+        <v>1.57</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46112.35416666666</v>
       </c>
       <c r="B32" t="n">
         <v>1.57</v>
       </c>
       <c r="C32" t="n">
-        <v>1.5702</v>
+        <v>1.5701</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46112.35486111111</v>
       </c>
       <c r="B33" t="n">
         <v>1.57</v>
       </c>
       <c r="C33" t="n">
-        <v>1.5701</v>
+        <v>1.5702</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46112.35555555556</v>
       </c>
       <c r="B34" t="n">
         <v>1.57</v>
       </c>
       <c r="C34" t="n">
-        <v>1.5702</v>
+        <v>1.5715</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0002</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46112.35625</v>
       </c>
       <c r="B35" t="n">
         <v>1.57</v>
       </c>
       <c r="C35" t="n">
-        <v>1.5761</v>
+        <v>1.5716</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0061</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46112.35694444444</v>
       </c>
       <c r="B36" t="n">
         <v>1.57</v>
       </c>
       <c r="C36" t="n">
-        <v>1.5812</v>
+        <v>1.5705</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0112</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46112.35763888889</v>
       </c>
       <c r="B37" t="n">
         <v>1.57</v>
       </c>
       <c r="C37" t="n">
-        <v>1.58</v>
+        <v>1.5716</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46112.35833333333</v>
       </c>
       <c r="B38" t="n">
         <v>1.57</v>
       </c>
       <c r="C38" t="n">
-        <v>1.58</v>
+        <v>1.5703</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46112.35902777778</v>
       </c>
       <c r="B39" t="n">
         <v>1.57</v>
       </c>
       <c r="C39" t="n">
-        <v>1.58</v>
+        <v>1.5706</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46112.35972222222</v>
       </c>
       <c r="B40" t="n">
         <v>1.57</v>
       </c>
       <c r="C40" t="n">
-        <v>1.5805</v>
+        <v>1.5742</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0105</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46112.36041666667</v>
       </c>
       <c r="B41" t="n">
         <v>1.58</v>
       </c>
       <c r="C41" t="n">
-        <v>1.5813</v>
+        <v>1.5794</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0013</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46112.36111111111</v>
       </c>
       <c r="B42" t="n">
@@ -1017,371 +1031,371 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46112.36180555556</v>
       </c>
       <c r="B43" t="n">
         <v>1.58</v>
       </c>
       <c r="C43" t="n">
-        <v>1.5834</v>
+        <v>1.5852</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0034</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46112.3625</v>
       </c>
       <c r="B44" t="n">
         <v>1.58</v>
       </c>
       <c r="C44" t="n">
-        <v>1.5895</v>
+        <v>1.5892</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0095</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46112.36319444444</v>
       </c>
       <c r="B45" t="n">
         <v>1.58</v>
       </c>
       <c r="C45" t="n">
-        <v>1.5915</v>
+        <v>1.5902</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0115</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46112.36388888889</v>
       </c>
       <c r="B46" t="n">
         <v>1.58</v>
       </c>
       <c r="C46" t="n">
-        <v>1.5927</v>
+        <v>1.5906</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0127</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46112.36458333334</v>
       </c>
       <c r="B47" t="n">
         <v>1.58</v>
       </c>
       <c r="C47" t="n">
-        <v>1.5989</v>
+        <v>1.5902</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0189</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46112.36527777778</v>
       </c>
       <c r="B48" t="n">
         <v>1.58</v>
       </c>
       <c r="C48" t="n">
-        <v>1.5998</v>
+        <v>1.5902</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0198</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46112.36597222222</v>
       </c>
       <c r="B49" t="n">
         <v>1.58</v>
       </c>
       <c r="C49" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="D49" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46112.36666666667</v>
       </c>
       <c r="B50" t="n">
         <v>1.58</v>
       </c>
       <c r="C50" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46112.36736111111</v>
       </c>
       <c r="B51" t="n">
         <v>1.58</v>
       </c>
       <c r="C51" t="n">
-        <v>1.6</v>
+        <v>1.5909</v>
       </c>
       <c r="D51" t="n">
-        <v>0.02</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46112.36805555555</v>
       </c>
       <c r="B52" t="n">
         <v>1.58</v>
       </c>
       <c r="C52" t="n">
-        <v>1.6002</v>
+        <v>1.5908</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0202</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46112.36875</v>
       </c>
       <c r="B53" t="n">
         <v>1.58</v>
       </c>
       <c r="C53" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="D53" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46112.36944444444</v>
       </c>
       <c r="B54" t="n">
         <v>1.59</v>
       </c>
       <c r="C54" t="n">
-        <v>1.6001</v>
+        <v>1.5921</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0101</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46112.37013888889</v>
       </c>
       <c r="B55" t="n">
         <v>1.59</v>
       </c>
       <c r="C55" t="n">
-        <v>1.6001</v>
+        <v>1.5921</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0101</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46112.37083333333</v>
       </c>
       <c r="B56" t="n">
         <v>1.59</v>
       </c>
       <c r="C56" t="n">
-        <v>1.6001</v>
+        <v>1.5947</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0101</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46112.37152777778</v>
       </c>
       <c r="B57" t="n">
         <v>1.59</v>
       </c>
       <c r="C57" t="n">
-        <v>1.6001</v>
+        <v>1.5954</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0101</v>
+        <v>0.0054</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46112.37222222222</v>
       </c>
       <c r="B58" t="n">
         <v>1.59</v>
       </c>
       <c r="C58" t="n">
-        <v>1.6003</v>
+        <v>1.6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0103</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46112.37291666667</v>
       </c>
       <c r="B59" t="n">
         <v>1.59</v>
       </c>
       <c r="C59" t="n">
-        <v>1.6051</v>
+        <v>1.5996</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0151</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46112.37361111111</v>
       </c>
       <c r="B60" t="n">
         <v>1.59</v>
       </c>
       <c r="C60" t="n">
-        <v>1.6055</v>
+        <v>1.6</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0155</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46112.37430555555</v>
       </c>
       <c r="B61" t="n">
         <v>1.59</v>
       </c>
       <c r="C61" t="n">
-        <v>1.6052</v>
+        <v>1.6016</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0152</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46112.375</v>
       </c>
       <c r="B62" t="n">
         <v>1.6</v>
       </c>
       <c r="C62" t="n">
-        <v>1.6072</v>
+        <v>1.6044</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0072</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46112.37569444445</v>
       </c>
       <c r="B63" t="n">
         <v>1.6</v>
       </c>
       <c r="C63" t="n">
-        <v>1.6075</v>
+        <v>1.6055</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0075</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46112.37638888889</v>
       </c>
       <c r="B64" t="n">
         <v>1.6</v>
       </c>
       <c r="C64" t="n">
-        <v>1.6085</v>
+        <v>1.6071</v>
       </c>
       <c r="D64" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46112.37708333333</v>
       </c>
       <c r="B65" t="n">
         <v>1.6</v>
       </c>
       <c r="C65" t="n">
-        <v>1.6102</v>
+        <v>1.6068</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0102</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46112.37777777778</v>
       </c>
       <c r="B66" t="n">
         <v>1.6</v>
       </c>
       <c r="C66" t="n">
-        <v>1.6109</v>
+        <v>1.6078</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0109</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46112.37847222222</v>
       </c>
       <c r="B67" t="n">
         <v>1.6</v>
       </c>
       <c r="C67" t="n">
-        <v>1.61</v>
+        <v>1.6105</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112.37916666667</v>
       </c>
       <c r="B68" t="n">
         <v>1.6</v>
       </c>
       <c r="C68" t="n">
-        <v>1.6105</v>
+        <v>1.6103</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0105</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112.37986111111</v>
       </c>
       <c r="B69" t="n">
@@ -1395,7 +1409,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46112.38055555556</v>
       </c>
       <c r="B70" t="n">
@@ -1409,7 +1423,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46112.38125</v>
       </c>
       <c r="B71" t="n">
@@ -1423,1557 +1437,1557 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46112.38194444445</v>
       </c>
       <c r="B72" t="n">
         <v>1.61</v>
       </c>
       <c r="C72" t="n">
-        <v>1.61</v>
+        <v>1.6103</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46112.38263888889</v>
       </c>
       <c r="B73" t="n">
         <v>1.61</v>
       </c>
       <c r="C73" t="n">
-        <v>1.6151</v>
+        <v>1.61</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46112.38333333333</v>
       </c>
       <c r="B74" t="n">
         <v>1.61</v>
       </c>
       <c r="C74" t="n">
-        <v>1.6144</v>
+        <v>1.61</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46112.38402777778</v>
       </c>
       <c r="B75" t="n">
         <v>1.61</v>
       </c>
       <c r="C75" t="n">
-        <v>1.6151</v>
+        <v>1.61</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46112.38472222222</v>
       </c>
       <c r="B76" t="n">
         <v>1.61</v>
       </c>
       <c r="C76" t="n">
-        <v>1.6184</v>
+        <v>1.6143</v>
       </c>
       <c r="D76" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46112.38541666666</v>
       </c>
       <c r="B77" t="n">
         <v>1.61</v>
       </c>
       <c r="C77" t="n">
-        <v>1.6204</v>
+        <v>1.6125</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0104</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46112.38611111111</v>
       </c>
       <c r="B78" t="n">
         <v>1.61</v>
       </c>
       <c r="C78" t="n">
-        <v>1.6202</v>
+        <v>1.6177</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0102</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46112.38680555556</v>
       </c>
       <c r="B79" t="n">
         <v>1.61</v>
       </c>
       <c r="C79" t="n">
-        <v>1.6204</v>
+        <v>1.6201</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0104</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46112.3875</v>
       </c>
       <c r="B80" t="n">
         <v>1.61</v>
       </c>
       <c r="C80" t="n">
-        <v>1.6206</v>
+        <v>1.62</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0106</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46112.38819444444</v>
       </c>
       <c r="B81" t="n">
         <v>1.61</v>
       </c>
       <c r="C81" t="n">
-        <v>1.6205</v>
+        <v>1.6222</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0105</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46112.38888888889</v>
       </c>
       <c r="B82" t="n">
         <v>1.61</v>
       </c>
       <c r="C82" t="n">
-        <v>1.6203</v>
+        <v>1.6202</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0103</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46112.38958333333</v>
       </c>
       <c r="B83" t="n">
         <v>1.62</v>
       </c>
       <c r="C83" t="n">
-        <v>1.6244</v>
+        <v>1.6211</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0044</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46112.39027777778</v>
       </c>
       <c r="B84" t="n">
         <v>1.62</v>
       </c>
       <c r="C84" t="n">
-        <v>1.6276</v>
+        <v>1.6231</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0076</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46112.39097222222</v>
       </c>
       <c r="B85" t="n">
         <v>1.62</v>
       </c>
       <c r="C85" t="n">
-        <v>1.63</v>
+        <v>1.6269</v>
       </c>
       <c r="D85" t="n">
-        <v>0.01</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46112.39166666667</v>
       </c>
       <c r="B86" t="n">
         <v>1.62</v>
       </c>
       <c r="C86" t="n">
-        <v>1.6332</v>
+        <v>1.6274</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0132</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46112.39236111111</v>
       </c>
       <c r="B87" t="n">
         <v>1.62</v>
       </c>
       <c r="C87" t="n">
-        <v>1.6393</v>
+        <v>1.6269</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0193</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46112.39305555556</v>
       </c>
       <c r="B88" t="n">
         <v>1.62</v>
       </c>
       <c r="C88" t="n">
-        <v>1.6403</v>
+        <v>1.6259</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0203</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46112.39375</v>
       </c>
       <c r="B89" t="n">
         <v>1.62</v>
       </c>
       <c r="C89" t="n">
-        <v>1.64</v>
+        <v>1.6261</v>
       </c>
       <c r="D89" t="n">
-        <v>0.02</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46112.39444444444</v>
       </c>
       <c r="B90" t="n">
         <v>1.62</v>
       </c>
       <c r="C90" t="n">
-        <v>1.6403</v>
+        <v>1.6266</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0203</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46112.39513888889</v>
       </c>
       <c r="B91" t="n">
         <v>1.62</v>
       </c>
       <c r="C91" t="n">
-        <v>1.6406</v>
+        <v>1.6272</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0206</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46112.39583333334</v>
       </c>
       <c r="B92" t="n">
         <v>1.62</v>
       </c>
       <c r="C92" t="n">
-        <v>1.6415</v>
+        <v>1.63</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0215</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46112.39652777778</v>
       </c>
       <c r="B93" t="n">
         <v>1.63</v>
       </c>
       <c r="C93" t="n">
-        <v>1.64</v>
+        <v>1.6301</v>
       </c>
       <c r="D93" t="n">
-        <v>0.01</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46112.39722222222</v>
       </c>
       <c r="B94" t="n">
         <v>1.63</v>
       </c>
       <c r="C94" t="n">
-        <v>1.6404</v>
+        <v>1.6318</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0104</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46112.39791666667</v>
       </c>
       <c r="B95" t="n">
         <v>1.63</v>
       </c>
       <c r="C95" t="n">
-        <v>1.6401</v>
+        <v>1.6318</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0101</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46112.39861111111</v>
       </c>
       <c r="B96" t="n">
         <v>1.63</v>
       </c>
       <c r="C96" t="n">
-        <v>1.6405</v>
+        <v>1.6315</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0105</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46112.39930555555</v>
       </c>
       <c r="B97" t="n">
         <v>1.63</v>
       </c>
       <c r="C97" t="n">
-        <v>1.6401</v>
+        <v>1.6307</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0101</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46112.4</v>
       </c>
       <c r="B98" t="n">
         <v>1.63</v>
       </c>
       <c r="C98" t="n">
-        <v>1.6402</v>
+        <v>1.6312</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0102</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46112.40069444444</v>
       </c>
       <c r="B99" t="n">
         <v>1.63</v>
       </c>
       <c r="C99" t="n">
-        <v>1.6411</v>
+        <v>1.6313</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0111</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46112.40138888889</v>
       </c>
       <c r="B100" t="n">
         <v>1.63</v>
       </c>
       <c r="C100" t="n">
-        <v>1.6422</v>
+        <v>1.636</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0122</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46112.40208333333</v>
       </c>
       <c r="B101" t="n">
         <v>1.63</v>
       </c>
       <c r="C101" t="n">
-        <v>1.6426</v>
+        <v>1.6401</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0126</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46112.40277777778</v>
       </c>
       <c r="B102" t="n">
         <v>1.63</v>
       </c>
       <c r="C102" t="n">
-        <v>1.6508</v>
+        <v>1.6401</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0208</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46112.40347222222</v>
       </c>
       <c r="B103" t="n">
         <v>1.63</v>
       </c>
       <c r="C103" t="n">
-        <v>1.65</v>
+        <v>1.6402</v>
       </c>
       <c r="D103" t="n">
-        <v>0.02</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46112.40416666667</v>
       </c>
       <c r="B104" t="n">
         <v>1.64</v>
       </c>
       <c r="C104" t="n">
-        <v>1.6512</v>
+        <v>1.6401</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0112</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46112.40486111111</v>
       </c>
       <c r="B105" t="n">
         <v>1.64</v>
       </c>
       <c r="C105" t="n">
-        <v>1.6506</v>
+        <v>1.6397</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0106</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46112.40555555555</v>
       </c>
       <c r="B106" t="n">
         <v>1.64</v>
       </c>
       <c r="C106" t="n">
-        <v>1.6521</v>
+        <v>1.6397</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0121</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46112.40625</v>
       </c>
       <c r="B107" t="n">
         <v>1.64</v>
       </c>
       <c r="C107" t="n">
-        <v>1.6519</v>
+        <v>1.6401</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0119</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46112.40694444445</v>
       </c>
       <c r="B108" t="n">
         <v>1.64</v>
       </c>
       <c r="C108" t="n">
-        <v>1.652</v>
+        <v>1.6428</v>
       </c>
       <c r="D108" t="n">
-        <v>0.012</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46112.40763888889</v>
       </c>
       <c r="B109" t="n">
         <v>1.64</v>
       </c>
       <c r="C109" t="n">
-        <v>1.6513</v>
+        <v>1.6497</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0113</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46112.40833333333</v>
       </c>
       <c r="B110" t="n">
         <v>1.64</v>
       </c>
       <c r="C110" t="n">
-        <v>1.6501</v>
+        <v>1.6518</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0101</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46112.40902777778</v>
       </c>
       <c r="B111" t="n">
         <v>1.64</v>
       </c>
       <c r="C111" t="n">
-        <v>1.6502</v>
+        <v>1.65</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0102</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46112.40972222222</v>
       </c>
       <c r="B112" t="n">
         <v>1.65</v>
       </c>
       <c r="C112" t="n">
-        <v>1.6502</v>
+        <v>1.6501</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46112.41041666667</v>
       </c>
       <c r="B113" t="n">
         <v>1.65</v>
       </c>
       <c r="C113" t="n">
-        <v>1.6517</v>
+        <v>1.6501</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0017</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46112.41111111111</v>
       </c>
       <c r="B114" t="n">
         <v>1.65</v>
       </c>
       <c r="C114" t="n">
-        <v>1.6567</v>
+        <v>1.6501</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0067</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46112.41180555556</v>
       </c>
       <c r="B115" t="n">
         <v>1.65</v>
       </c>
       <c r="C115" t="n">
-        <v>1.6561</v>
+        <v>1.6504</v>
       </c>
       <c r="D115" t="n">
-        <v>0.0061</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46112.4125</v>
       </c>
       <c r="B116" t="n">
         <v>1.65</v>
       </c>
       <c r="C116" t="n">
-        <v>1.6579</v>
+        <v>1.6519</v>
       </c>
       <c r="D116" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46112.41319444445</v>
       </c>
       <c r="B117" t="n">
         <v>1.65</v>
       </c>
       <c r="C117" t="n">
-        <v>1.6644</v>
+        <v>1.6516</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0144</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46112.41388888889</v>
       </c>
       <c r="B118" t="n">
         <v>1.65</v>
       </c>
       <c r="C118" t="n">
-        <v>1.6651</v>
+        <v>1.6502</v>
       </c>
       <c r="D118" t="n">
-        <v>0.0151</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46112.41458333333</v>
       </c>
       <c r="B119" t="n">
         <v>1.65</v>
       </c>
       <c r="C119" t="n">
-        <v>1.668</v>
+        <v>1.6518</v>
       </c>
       <c r="D119" t="n">
-        <v>0.018</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46112.41527777778</v>
       </c>
       <c r="B120" t="n">
         <v>1.65</v>
       </c>
       <c r="C120" t="n">
-        <v>1.6707</v>
+        <v>1.6564</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0207</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46112.41597222222</v>
       </c>
       <c r="B121" t="n">
         <v>1.65</v>
       </c>
       <c r="C121" t="n">
-        <v>1.6708</v>
+        <v>1.6549</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0208</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46112.41666666666</v>
       </c>
       <c r="B122" t="n">
         <v>1.65</v>
       </c>
       <c r="C122" t="n">
-        <v>1.6707</v>
+        <v>1.6566</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0207</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46112.41736111111</v>
       </c>
       <c r="B123" t="n">
         <v>1.65</v>
       </c>
       <c r="C123" t="n">
-        <v>1.6702</v>
+        <v>1.6591</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0202</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112.41805555556</v>
       </c>
       <c r="B124" t="n">
         <v>1.66</v>
       </c>
       <c r="C124" t="n">
-        <v>1.6706</v>
+        <v>1.6608</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0106</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46112.41875</v>
       </c>
       <c r="B125" t="n">
         <v>1.66</v>
       </c>
       <c r="C125" t="n">
-        <v>1.6706</v>
+        <v>1.6608</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0106</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46112.41944444444</v>
       </c>
       <c r="B126" t="n">
         <v>1.66</v>
       </c>
       <c r="C126" t="n">
-        <v>1.6706</v>
+        <v>1.6601</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0106</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46112.42013888889</v>
       </c>
       <c r="B127" t="n">
         <v>1.66</v>
       </c>
       <c r="C127" t="n">
-        <v>1.6701</v>
+        <v>1.6602</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0101</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46112.42083333333</v>
       </c>
       <c r="B128" t="n">
         <v>1.66</v>
       </c>
       <c r="C128" t="n">
-        <v>1.6704</v>
+        <v>1.6601</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0104</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46112.42152777778</v>
       </c>
       <c r="B129" t="n">
         <v>1.66</v>
       </c>
       <c r="C129" t="n">
-        <v>1.6661</v>
+        <v>1.6602</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0061</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112.42222222222</v>
       </c>
       <c r="B130" t="n">
         <v>1.66</v>
       </c>
       <c r="C130" t="n">
-        <v>1.6643</v>
+        <v>1.6646</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0043</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46112.42291666667</v>
       </c>
       <c r="B131" t="n">
         <v>1.66</v>
       </c>
       <c r="C131" t="n">
-        <v>1.6654</v>
+        <v>1.6661</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0054</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46112.42361111111</v>
       </c>
       <c r="B132" t="n">
         <v>1.66</v>
       </c>
       <c r="C132" t="n">
-        <v>1.6599</v>
+        <v>1.6684</v>
       </c>
       <c r="D132" t="n">
-        <v>0.0001</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46112.42430555556</v>
       </c>
       <c r="B133" t="n">
         <v>1.66</v>
       </c>
       <c r="C133" t="n">
-        <v>1.6594</v>
+        <v>1.6702</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46112.425</v>
       </c>
       <c r="B134" t="n">
         <v>1.66</v>
       </c>
       <c r="C134" t="n">
-        <v>1.6538</v>
+        <v>1.6701</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0062</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46112.42569444444</v>
       </c>
       <c r="B135" t="n">
         <v>1.66</v>
       </c>
       <c r="C135" t="n">
-        <v>1.6514</v>
+        <v>1.6702</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0086</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46112.42638888889</v>
       </c>
       <c r="B136" t="n">
         <v>1.67</v>
       </c>
       <c r="C136" t="n">
-        <v>1.649</v>
+        <v>1.67</v>
       </c>
       <c r="D136" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46112.42708333334</v>
       </c>
       <c r="B137" t="n">
         <v>1.67</v>
       </c>
       <c r="C137" t="n">
-        <v>1.6479</v>
+        <v>1.6704</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0221</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46112.42777777778</v>
       </c>
       <c r="B138" t="n">
         <v>1.67</v>
       </c>
       <c r="C138" t="n">
-        <v>1.6435</v>
+        <v>1.6702</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0265</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46112.42847222222</v>
       </c>
       <c r="B139" t="n">
         <v>1.67</v>
       </c>
       <c r="C139" t="n">
-        <v>1.643</v>
+        <v>1.6701</v>
       </c>
       <c r="D139" t="n">
-        <v>0.027</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46112.42916666667</v>
       </c>
       <c r="B140" t="n">
         <v>1.67</v>
       </c>
       <c r="C140" t="n">
-        <v>1.6406</v>
+        <v>1.6737</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0294</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46112.42986111111</v>
       </c>
       <c r="B141" t="n">
         <v>1.67</v>
       </c>
       <c r="C141" t="n">
-        <v>1.639</v>
+        <v>1.6774</v>
       </c>
       <c r="D141" t="n">
-        <v>0.031</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46112.43055555555</v>
       </c>
       <c r="B142" t="n">
         <v>1.67</v>
       </c>
       <c r="C142" t="n">
-        <v>1.6383</v>
+        <v>1.6802</v>
       </c>
       <c r="D142" t="n">
-        <v>0.0317</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46112.43125</v>
       </c>
       <c r="B143" t="n">
         <v>1.67</v>
       </c>
       <c r="C143" t="n">
-        <v>1.6334</v>
+        <v>1.6808</v>
       </c>
       <c r="D143" t="n">
-        <v>0.0366</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46112.43194444444</v>
       </c>
       <c r="B144" t="n">
         <v>1.67</v>
       </c>
       <c r="C144" t="n">
-        <v>1.6366</v>
+        <v>1.6805</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0334</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46112.43263888889</v>
       </c>
       <c r="B145" t="n">
         <v>1.67</v>
       </c>
       <c r="C145" t="n">
-        <v>1.6326</v>
+        <v>1.6801</v>
       </c>
       <c r="D145" t="n">
-        <v>0.0374</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46112.43333333333</v>
       </c>
       <c r="B146" t="n">
         <v>1.67</v>
       </c>
       <c r="C146" t="n">
-        <v>1.6354</v>
+        <v>1.6803</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0346</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46112.43402777778</v>
       </c>
       <c r="B147" t="n">
         <v>1.67</v>
       </c>
       <c r="C147" t="n">
-        <v>1.6324</v>
+        <v>1.6804</v>
       </c>
       <c r="D147" t="n">
-        <v>0.0376</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46112.43472222222</v>
       </c>
       <c r="B148" t="n">
         <v>1.68</v>
       </c>
       <c r="C148" t="n">
-        <v>1.6211</v>
+        <v>1.68</v>
       </c>
       <c r="D148" t="n">
-        <v>0.0589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46112.43541666667</v>
       </c>
       <c r="B149" t="n">
         <v>1.67</v>
       </c>
       <c r="C149" t="n">
-        <v>1.62</v>
+        <v>1.6741</v>
       </c>
       <c r="D149" t="n">
-        <v>0.05</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46112.43611111111</v>
       </c>
       <c r="B150" t="n">
         <v>1.67</v>
       </c>
       <c r="C150" t="n">
-        <v>1.613</v>
+        <v>1.6757</v>
       </c>
       <c r="D150" t="n">
-        <v>0.057</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46112.43680555555</v>
       </c>
       <c r="B151" t="n">
         <v>1.67</v>
       </c>
       <c r="C151" t="n">
-        <v>1.6094</v>
+        <v>1.6759</v>
       </c>
       <c r="D151" t="n">
-        <v>0.0606</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46112.4375</v>
       </c>
       <c r="B152" t="n">
         <v>1.67</v>
       </c>
       <c r="C152" t="n">
-        <v>1.6088</v>
+        <v>1.6761</v>
       </c>
       <c r="D152" t="n">
-        <v>0.0612</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46112.43819444445</v>
       </c>
       <c r="B153" t="n">
         <v>1.66</v>
       </c>
       <c r="C153" t="n">
-        <v>1.6083</v>
+        <v>1.6761</v>
       </c>
       <c r="D153" t="n">
-        <v>0.0517</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46112.43888888889</v>
       </c>
       <c r="B154" t="n">
         <v>1.66</v>
       </c>
       <c r="C154" t="n">
-        <v>1.6047</v>
+        <v>1.677</v>
       </c>
       <c r="D154" t="n">
-        <v>0.0553</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46112.43958333333</v>
       </c>
       <c r="B155" t="n">
         <v>1.66</v>
       </c>
       <c r="C155" t="n">
-        <v>1.6007</v>
+        <v>1.6756</v>
       </c>
       <c r="D155" t="n">
-        <v>0.0593</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46112.44027777778</v>
       </c>
       <c r="B156" t="n">
         <v>1.66</v>
       </c>
       <c r="C156" t="n">
-        <v>1.599</v>
+        <v>1.676</v>
       </c>
       <c r="D156" t="n">
-        <v>0.061</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46112.44097222222</v>
       </c>
       <c r="B157" t="n">
         <v>1.66</v>
       </c>
       <c r="C157" t="n">
-        <v>1.5999</v>
+        <v>1.6751</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0601</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46112.44166666667</v>
       </c>
       <c r="B158" t="n">
         <v>1.65</v>
       </c>
       <c r="C158" t="n">
-        <v>1.5931</v>
+        <v>1.6748</v>
       </c>
       <c r="D158" t="n">
-        <v>0.0569</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46112.44236111111</v>
       </c>
       <c r="B159" t="n">
         <v>1.65</v>
       </c>
       <c r="C159" t="n">
-        <v>1.5934</v>
+        <v>1.6731</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0566</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46112.44305555556</v>
       </c>
       <c r="B160" t="n">
         <v>1.65</v>
       </c>
       <c r="C160" t="n">
-        <v>1.5915</v>
+        <v>1.6712</v>
       </c>
       <c r="D160" t="n">
-        <v>0.0585</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46112.44375</v>
       </c>
       <c r="B161" t="n">
         <v>1.65</v>
       </c>
       <c r="C161" t="n">
-        <v>1.5889</v>
+        <v>1.6625</v>
       </c>
       <c r="D161" t="n">
-        <v>0.0611</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46112.44444444445</v>
       </c>
       <c r="B162" t="n">
         <v>1.64</v>
       </c>
       <c r="C162" t="n">
-        <v>1.5878</v>
+        <v>1.6652</v>
       </c>
       <c r="D162" t="n">
-        <v>0.0522</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46112.44513888889</v>
       </c>
       <c r="B163" t="n">
         <v>1.64</v>
       </c>
       <c r="C163" t="n">
-        <v>1.5868</v>
+        <v>1.6617</v>
       </c>
       <c r="D163" t="n">
-        <v>0.0532</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46112.44583333333</v>
       </c>
       <c r="B164" t="n">
         <v>1.64</v>
       </c>
       <c r="C164" t="n">
-        <v>1.5806</v>
+        <v>1.6586</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0594</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46112.44652777778</v>
       </c>
       <c r="B165" t="n">
         <v>1.64</v>
       </c>
       <c r="C165" t="n">
-        <v>1.58</v>
+        <v>1.6579</v>
       </c>
       <c r="D165" t="n">
-        <v>0.06</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46112.44722222222</v>
       </c>
       <c r="B166" t="n">
         <v>1.64</v>
       </c>
       <c r="C166" t="n">
-        <v>1.5767</v>
+        <v>1.6545</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0633</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46112.44791666666</v>
       </c>
       <c r="B167" t="n">
         <v>1.63</v>
       </c>
       <c r="C167" t="n">
-        <v>1.579</v>
+        <v>1.6495</v>
       </c>
       <c r="D167" t="n">
-        <v>0.051</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46112.44861111111</v>
       </c>
       <c r="B168" t="n">
         <v>1.63</v>
       </c>
       <c r="C168" t="n">
-        <v>1.571</v>
+        <v>1.6477</v>
       </c>
       <c r="D168" t="n">
-        <v>0.059</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46112.44930555556</v>
       </c>
       <c r="B169" t="n">
         <v>1.63</v>
       </c>
       <c r="C169" t="n">
-        <v>1.57</v>
+        <v>1.6434</v>
       </c>
       <c r="D169" t="n">
-        <v>0.06</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46112.45</v>
       </c>
       <c r="B170" t="n">
         <v>1.63</v>
       </c>
       <c r="C170" t="n">
-        <v>1.5668</v>
+        <v>1.6432</v>
       </c>
       <c r="D170" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46112.45069444444</v>
       </c>
       <c r="B171" t="n">
         <v>1.62</v>
       </c>
       <c r="C171" t="n">
-        <v>1.5621</v>
+        <v>1.6392</v>
       </c>
       <c r="D171" t="n">
-        <v>0.0579</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46112.45138888889</v>
       </c>
       <c r="B172" t="n">
         <v>1.62</v>
       </c>
       <c r="C172" t="n">
-        <v>1.5557</v>
+        <v>1.6374</v>
       </c>
       <c r="D172" t="n">
-        <v>0.0643</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46112.45208333333</v>
       </c>
       <c r="B173" t="n">
         <v>1.62</v>
       </c>
       <c r="C173" t="n">
-        <v>1.5569</v>
+        <v>1.6322</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0631</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46112.45277777778</v>
       </c>
       <c r="B174" t="n">
         <v>1.62</v>
       </c>
       <c r="C174" t="n">
-        <v>1.5523</v>
+        <v>1.6288</v>
       </c>
       <c r="D174" t="n">
-        <v>0.0677</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46112.45347222222</v>
       </c>
       <c r="B175" t="n">
         <v>1.62</v>
       </c>
       <c r="C175" t="n">
-        <v>1.5497</v>
+        <v>1.6286</v>
       </c>
       <c r="D175" t="n">
-        <v>0.0703</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46112.45416666667</v>
       </c>
       <c r="B176" t="n">
         <v>1.61</v>
       </c>
       <c r="C176" t="n">
-        <v>1.55</v>
+        <v>1.6239</v>
       </c>
       <c r="D176" t="n">
-        <v>0.06</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46112.45486111111</v>
       </c>
       <c r="B177" t="n">
         <v>1.61</v>
       </c>
       <c r="C177" t="n">
-        <v>1.5501</v>
+        <v>1.6213</v>
       </c>
       <c r="D177" t="n">
-        <v>0.0599</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46112.45555555556</v>
       </c>
       <c r="B178" t="n">
         <v>1.61</v>
       </c>
       <c r="C178" t="n">
-        <v>1.5498</v>
+        <v>1.6199</v>
       </c>
       <c r="D178" t="n">
-        <v>0.0602</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46112.45625</v>
       </c>
       <c r="B179" t="n">
         <v>1.61</v>
       </c>
       <c r="C179" t="n">
-        <v>1.55</v>
+        <v>1.6126</v>
       </c>
       <c r="D179" t="n">
-        <v>0.06</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46112.45694444444</v>
       </c>
       <c r="B180" t="n">
         <v>1.6</v>
       </c>
       <c r="C180" t="n">
-        <v>1.55</v>
+        <v>1.6096</v>
       </c>
       <c r="D180" t="n">
-        <v>0.05</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46112.45763888889</v>
       </c>
       <c r="B181" t="n">
         <v>1.6</v>
       </c>
       <c r="C181" t="n">
-        <v>1.55</v>
+        <v>1.6091</v>
       </c>
       <c r="D181" t="n">
-        <v>0.05</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46112.45833333334</v>
       </c>
       <c r="B182" t="n">
         <v>1.6</v>
       </c>
       <c r="C182" t="n">
-        <v>1.55</v>
+        <v>1.6073</v>
       </c>
       <c r="D182" t="n">
-        <v>0.05</v>
+        <v>0.0073</v>
       </c>
     </row>
   </sheetData>
